--- a/ig/nr/3.0.1/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr/3.0.1/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$104</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:11:02+00:00</t>
+    <t>2023-04-26T08:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,6 +326,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -400,10 +404,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -460,14 +460,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesFrObservationBodyHeight</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2448,12 +2441,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP105"/>
+  <dimension ref="A1:AP104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.37109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2875,7 +2868,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>88</v>
@@ -2959,7 +2952,7 @@
         <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2971,7 +2964,7 @@
         <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>78</v>
@@ -2982,10 +2975,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -3008,13 +3001,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -3065,7 +3058,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3089,7 +3082,7 @@
         <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>78</v>
@@ -3100,14 +3093,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3126,16 +3119,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3173,19 +3166,19 @@
         <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -3197,7 +3190,7 @@
         <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -3209,7 +3202,7 @@
         <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>78</v>
@@ -3220,10 +3213,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3249,13 +3242,13 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3305,7 +3298,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3317,7 +3310,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -3329,7 +3322,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -3437,7 +3430,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -3449,7 +3442,7 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3557,7 +3550,7 @@
         <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -3569,7 +3562,7 @@
         <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>78</v>
@@ -3591,7 +3584,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -3653,17 +3646,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3675,7 +3670,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -3687,7 +3682,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>78</v>
@@ -3698,26 +3693,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
@@ -3726,16 +3719,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3746,7 +3739,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3761,13 +3754,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -3785,7 +3778,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3797,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -3806,10 +3799,10 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3820,10 +3813,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3846,16 +3839,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3881,13 +3874,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3905,7 +3898,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3917,7 +3910,7 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
@@ -3926,10 +3919,10 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3940,10 +3933,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3954,28 +3947,28 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4001,13 +3994,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -4025,19 +4018,19 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -4046,10 +4039,10 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -4060,10 +4053,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4080,22 +4073,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4121,13 +4114,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -4145,7 +4138,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4157,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4169,7 +4162,7 @@
         <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -4180,14 +4173,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4206,16 +4199,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4241,13 +4234,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4265,7 +4258,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4277,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4289,7 +4282,7 @@
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -4300,21 +4293,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -4326,16 +4319,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4385,19 +4378,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -4409,7 +4402,7 @@
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -4420,14 +4413,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4446,16 +4439,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4493,19 +4486,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4514,10 +4507,10 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -4529,7 +4522,7 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -4540,21 +4533,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -4566,17 +4561,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4613,19 +4606,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4637,7 +4630,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -4649,7 +4642,7 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4660,16 +4653,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4679,7 +4672,7 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
@@ -4688,15 +4681,17 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4745,7 +4740,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4757,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -4769,7 +4764,7 @@
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4780,46 +4775,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4855,19 +4850,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4879,7 +4874,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -4891,7 +4886,7 @@
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4902,14 +4897,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4922,25 +4917,23 @@
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4977,19 +4970,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -5001,22 +4994,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>78</v>
@@ -5024,14 +5017,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5050,17 +5043,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -5109,7 +5104,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5121,22 +5116,22 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>78</v>
@@ -5144,14 +5139,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5170,20 +5165,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5231,7 +5224,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5243,19 +5236,19 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -5266,44 +5259,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5327,13 +5322,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5351,34 +5346,34 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>78</v>
@@ -5386,10 +5381,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5400,31 +5395,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5449,58 +5444,56 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>78</v>
@@ -5508,12 +5501,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5522,7 +5517,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>89</v>
@@ -5534,19 +5529,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5571,29 +5566,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5605,7 +5602,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5614,13 +5611,13 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>78</v>
@@ -5631,23 +5628,21 @@
         <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>265</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5656,20 +5651,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5693,13 +5684,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5717,19 +5708,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5738,13 +5729,13 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>78</v>
@@ -5759,14 +5750,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5778,15 +5769,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5823,31 +5816,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5859,7 +5852,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5877,37 +5870,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5943,19 +5938,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5967,7 +5962,7 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5976,10 +5971,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5990,10 +5985,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6001,35 +5996,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -6077,19 +6068,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -6098,10 +6089,10 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -6119,14 +6110,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -6138,15 +6129,17 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6183,31 +6176,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -6219,7 +6212,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -6237,43 +6230,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6303,31 +6298,31 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -6336,10 +6331,10 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6350,10 +6345,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6361,13 +6356,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -6376,26 +6371,24 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -6437,7 +6430,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6449,7 +6442,7 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -6458,10 +6451,10 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6472,10 +6465,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6483,13 +6476,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -6498,24 +6491,26 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6557,7 +6552,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6569,7 +6564,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -6578,10 +6573,10 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6592,10 +6587,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6603,13 +6598,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -6618,26 +6613,26 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6679,7 +6674,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6691,7 +6686,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -6700,10 +6695,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6714,10 +6709,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6740,19 +6735,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6801,7 +6796,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6813,7 +6808,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6822,10 +6817,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6836,10 +6831,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6862,19 +6857,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6923,7 +6918,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6935,7 +6930,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -6944,10 +6939,10 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6958,24 +6953,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6984,19 +6979,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7021,13 +7016,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -7045,10 +7040,10 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -7057,69 +7052,65 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -7143,13 +7134,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7167,56 +7158,56 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -7228,15 +7219,17 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7273,31 +7266,31 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -7309,7 +7302,7 @@
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -7320,14 +7313,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7343,21 +7336,23 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7393,19 +7388,17 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7417,7 +7410,7 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -7426,10 +7419,10 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7443,18 +7436,20 @@
         <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7466,19 +7461,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7515,17 +7510,19 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7537,7 +7534,7 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -7546,10 +7543,10 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7563,17 +7560,15 @@
         <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C43" t="s" s="2">
         <v>357</v>
       </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
@@ -7585,23 +7580,19 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7649,19 +7640,19 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -7670,10 +7661,10 @@
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7691,14 +7682,14 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7710,15 +7701,17 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7755,31 +7748,31 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
@@ -7791,7 +7784,7 @@
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7809,14 +7802,14 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7825,27 +7818,29 @@
         <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>78</v>
+        <v>362</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>78</v>
@@ -7875,31 +7870,31 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -7908,10 +7903,10 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7922,10 +7917,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7933,7 +7928,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -7948,26 +7943,24 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>364</v>
+        <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>78</v>
@@ -8009,7 +8002,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -8021,7 +8014,7 @@
         <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
@@ -8030,10 +8023,10 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8055,7 +8048,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
@@ -8070,24 +8063,26 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>78</v>
@@ -8129,7 +8124,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8141,7 +8136,7 @@
         <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
@@ -8150,10 +8145,10 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8164,10 +8159,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8175,7 +8170,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
@@ -8190,26 +8185,26 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>78</v>
@@ -8251,7 +8246,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -8263,7 +8258,7 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
@@ -8272,10 +8267,10 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -8312,19 +8307,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8373,7 +8368,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8385,7 +8380,7 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
@@ -8394,10 +8389,10 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8411,7 +8406,7 @@
         <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8434,19 +8429,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8495,7 +8490,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8507,7 +8502,7 @@
         <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>78</v>
@@ -8516,10 +8511,10 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8530,10 +8525,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8541,13 +8536,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
@@ -8556,19 +8551,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8617,7 +8612,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8629,22 +8624,22 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>78</v>
@@ -8652,10 +8647,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8663,13 +8658,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -8678,20 +8673,18 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8739,34 +8732,34 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>78</v>
@@ -8774,21 +8767,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -8800,18 +8793,20 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8859,34 +8854,34 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>78</v>
@@ -8894,24 +8889,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>78</v>
@@ -8920,19 +8915,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8981,7 +8976,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8990,25 +8985,25 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>100</v>
+        <v>407</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>226</v>
+        <v>408</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>78</v>
@@ -9016,24 +9011,24 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
@@ -9042,20 +9037,18 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>126</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -9103,7 +9096,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -9112,25 +9105,25 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>409</v>
+        <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>410</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>78</v>
@@ -9138,10 +9131,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9152,7 +9145,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -9164,18 +9157,20 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>126</v>
+        <v>421</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -9223,34 +9218,34 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>78</v>
@@ -9258,10 +9253,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9272,10 +9267,10 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -9284,19 +9279,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>224</v>
+        <v>432</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -9333,59 +9328,59 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>100</v>
+        <v>436</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9406,19 +9401,19 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9428,7 +9423,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9455,17 +9450,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -9474,40 +9471,38 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9519,29 +9514,25 @@
         <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>432</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>105</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9550,7 +9541,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -9589,7 +9580,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9598,28 +9589,28 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>441</v>
+        <v>108</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9631,14 +9622,14 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9650,15 +9641,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9695,31 +9688,31 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9731,7 +9724,7 @@
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9749,37 +9742,39 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>111</v>
+        <v>451</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>112</v>
+        <v>452</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9815,31 +9810,31 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>117</v>
+        <v>455</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9848,10 +9843,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>101</v>
+        <v>457</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9862,10 +9857,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9873,39 +9868,41 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>452</v>
+        <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>455</v>
+        <v>303</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="R62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9925,13 +9922,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>464</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9949,7 +9946,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9961,7 +9958,7 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9970,10 +9967,10 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9984,10 +9981,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9995,41 +9992,39 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>465</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>78</v>
       </c>
@@ -10049,13 +10044,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>466</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -10073,7 +10068,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -10085,7 +10080,7 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -10094,10 +10089,10 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -10108,10 +10103,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10134,26 +10129,26 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>305</v>
+        <v>481</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>78</v>
@@ -10195,7 +10190,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -10204,10 +10199,10 @@
         <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>485</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -10216,10 +10211,10 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10230,10 +10225,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10256,26 +10251,26 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>78</v>
@@ -10293,13 +10288,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -10317,7 +10312,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10326,10 +10321,10 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>487</v>
+        <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -10338,10 +10333,10 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10352,10 +10347,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10363,7 +10358,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>88</v>
@@ -10375,22 +10370,22 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10415,13 +10410,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10448,10 +10443,10 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>100</v>
+        <v>503</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10460,10 +10455,10 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>477</v>
+        <v>102</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10474,10 +10469,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10491,7 +10486,7 @@
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>78</v>
@@ -10500,20 +10495,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -10537,13 +10528,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10561,7 +10552,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10570,10 +10561,10 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -10582,10 +10573,10 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>506</v>
+        <v>108</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10596,21 +10587,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10622,15 +10613,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10667,31 +10660,31 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10703,7 +10696,7 @@
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10714,14 +10707,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10737,21 +10730,23 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10787,19 +10782,19 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10811,7 +10806,7 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10820,10 +10815,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10834,10 +10829,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10848,7 +10843,7 @@
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10857,23 +10852,19 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10921,19 +10912,19 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -10942,10 +10933,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10956,21 +10947,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10982,15 +10973,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11027,31 +11020,31 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -11063,7 +11056,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -11074,21 +11067,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -11097,21 +11090,23 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -11147,31 +11142,31 @@
         <v>78</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -11180,10 +11175,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -11194,10 +11189,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11205,7 +11200,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>88</v>
@@ -11220,20 +11215,18 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -11281,7 +11274,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -11293,7 +11286,7 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -11302,10 +11295,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -11316,10 +11309,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11327,7 +11320,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>88</v>
@@ -11342,18 +11335,20 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -11401,7 +11396,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11413,7 +11408,7 @@
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11422,10 +11417,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11436,10 +11431,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11447,7 +11442,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -11462,19 +11457,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11523,7 +11518,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11535,7 +11530,7 @@
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11544,10 +11539,10 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11558,10 +11553,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11584,19 +11579,19 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11645,7 +11640,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11657,7 +11652,7 @@
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11666,10 +11661,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11680,10 +11675,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11706,19 +11701,19 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11767,7 +11762,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11779,7 +11774,7 @@
         <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11788,10 +11783,10 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11802,21 +11797,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11825,22 +11820,22 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>331</v>
+        <v>518</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>332</v>
+        <v>519</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>333</v>
+        <v>520</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>334</v>
+        <v>521</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11865,13 +11860,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11889,49 +11884,49 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>335</v>
+        <v>516</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>336</v>
+        <v>525</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>337</v>
+        <v>526</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11950,19 +11945,19 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>529</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11987,13 +11982,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -12011,7 +12006,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -12023,33 +12018,33 @@
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12060,7 +12055,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -12072,20 +12067,18 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>531</v>
+        <v>251</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -12109,13 +12102,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -12133,45 +12126,45 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>78</v>
+        <v>542</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12194,18 +12187,20 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -12229,13 +12224,13 @@
         <v>78</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>160</v>
+        <v>242</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>78</v>
@@ -12253,7 +12248,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -12265,33 +12260,33 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>544</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12314,20 +12309,18 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>253</v>
+        <v>556</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -12351,13 +12344,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>553</v>
+        <v>78</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -12375,7 +12368,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -12387,33 +12380,33 @@
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>78</v>
+        <v>560</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12436,16 +12429,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12495,7 +12488,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12507,33 +12500,33 @@
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12544,7 +12537,7 @@
         <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12556,18 +12549,20 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12615,45 +12610,45 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>226</v>
+        <v>579</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12664,7 +12659,7 @@
         <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -12676,20 +12671,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>576</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>577</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12737,19 +12728,19 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>575</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12758,10 +12749,10 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>582</v>
+        <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>583</v>
+        <v>108</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12772,21 +12763,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12798,15 +12789,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12843,31 +12836,31 @@
         <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12879,7 +12872,7 @@
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12890,14 +12883,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12910,24 +12903,26 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>111</v>
+        <v>586</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>112</v>
+        <v>587</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12963,19 +12958,19 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>117</v>
+        <v>588</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12987,7 +12982,7 @@
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12999,7 +12994,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13010,46 +13005,44 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>590</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -13097,19 +13090,19 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>100</v>
+        <v>594</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>118</v>
+        <v>595</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -13118,10 +13111,10 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>101</v>
+        <v>597</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>78</v>
@@ -13132,10 +13125,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13158,16 +13151,16 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13217,7 +13210,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -13226,22 +13219,22 @@
         <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ89" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN89" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -13252,10 +13245,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13278,18 +13271,20 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>592</v>
+        <v>251</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -13313,13 +13308,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>78</v>
+        <v>607</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>78</v>
+        <v>608</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -13337,7 +13332,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -13346,22 +13341,22 @@
         <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>596</v>
+        <v>100</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>597</v>
+        <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>78</v>
+        <v>609</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>603</v>
+        <v>526</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
@@ -13372,10 +13367,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13386,7 +13381,7 @@
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -13398,19 +13393,19 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13435,13 +13430,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13459,31 +13454,31 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
@@ -13494,10 +13489,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13508,7 +13503,7 @@
         <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -13520,19 +13515,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>619</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13557,55 +13552,55 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>124</v>
+        <v>624</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>611</v>
+        <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>528</v>
+        <v>626</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
@@ -13616,10 +13611,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13642,20 +13637,18 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>621</v>
+        <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13703,7 +13696,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13715,7 +13708,7 @@
         <v>100</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>626</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13724,10 +13717,10 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13738,10 +13731,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13752,7 +13745,7 @@
         <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13761,19 +13754,19 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>632</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>305</v>
+        <v>635</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13823,19 +13816,19 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13844,10 +13837,10 @@
         <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>598</v>
+        <v>636</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13858,10 +13851,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13884,16 +13877,16 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13943,7 +13936,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13955,7 +13948,7 @@
         <v>100</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13964,10 +13957,10 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13978,10 +13971,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13995,7 +13988,7 @@
         <v>77</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>78</v>
@@ -14004,18 +13997,20 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>641</v>
+        <v>574</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>646</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>647</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -14063,7 +14058,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -14075,7 +14070,7 @@
         <v>100</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>226</v>
+        <v>648</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -14084,10 +14079,10 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14098,10 +14093,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14112,32 +14107,28 @@
         <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>647</v>
+        <v>105</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -14185,19 +14176,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>646</v>
+        <v>107</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>650</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -14206,10 +14197,10 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>651</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>652</v>
+        <v>108</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>78</v>
@@ -14220,21 +14211,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -14246,15 +14237,17 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -14291,31 +14284,31 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -14327,7 +14320,7 @@
         <v>78</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>78</v>
@@ -14338,14 +14331,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14358,24 +14351,26 @@
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>111</v>
+        <v>586</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>112</v>
+        <v>587</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
@@ -14411,19 +14406,19 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>117</v>
+        <v>588</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -14435,7 +14430,7 @@
         <v>100</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -14447,7 +14442,7 @@
         <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>78</v>
@@ -14458,45 +14453,45 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>588</v>
+        <v>655</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>589</v>
+        <v>656</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>113</v>
+        <v>657</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>208</v>
+        <v>658</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14521,13 +14516,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14545,34 +14540,34 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>590</v>
+        <v>654</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>78</v>
+        <v>659</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>101</v>
+        <v>347</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>78</v>
@@ -14580,10 +14575,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14591,7 +14586,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>88</v>
@@ -14606,19 +14601,19 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>253</v>
+        <v>661</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>660</v>
+        <v>433</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14643,13 +14638,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>344</v>
+        <v>665</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>345</v>
+        <v>666</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14667,45 +14662,45 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>100</v>
+        <v>667</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>348</v>
+        <v>438</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>349</v>
+        <v>439</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14725,22 +14720,22 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>663</v>
+        <v>251</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>435</v>
+        <v>500</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14765,13 +14760,13 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>667</v>
+        <v>501</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>668</v>
+        <v>502</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -14789,7 +14784,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14798,50 +14793,50 @@
         <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>670</v>
+        <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>440</v>
+        <v>102</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>441</v>
+        <v>504</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
@@ -14850,19 +14845,19 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>672</v>
+        <v>518</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>673</v>
+        <v>519</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>674</v>
+        <v>520</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14887,13 +14882,13 @@
         <v>78</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>504</v>
+        <v>675</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14911,37 +14906,37 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>675</v>
+        <v>100</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>101</v>
+        <v>525</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -14953,7 +14948,7 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14972,19 +14967,19 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>520</v>
+        <v>677</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>521</v>
+        <v>678</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>523</v>
+        <v>578</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -15009,13 +15004,13 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>677</v>
+        <v>78</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -15042,154 +15037,32 @@
         <v>77</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>527</v>
+        <v>580</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP105" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP105">
+  <autoFilter ref="A1:AP104">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15199,7 +15072,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI103">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
